--- a/legenda_alvos.xlsx
+++ b/legenda_alvos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="142">
   <si>
     <t xml:space="preserve">Grupo</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t xml:space="preserve">Estruturas de Mineração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo</t>
   </si>
 </sst>
 </file>
@@ -1786,6 +1789,14 @@
         <v>140</v>
       </c>
     </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
